--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>198</v>
+        <v>102</v>
       </c>
       <c r="D2">
-        <v>92</v>
+        <v>299</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="D3">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="E3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>215</v>
       </c>
       <c r="D3">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H3">
         <v>426</v>
